--- a/__EXCEL/excelproj2/Courses.xlsx
+++ b/__EXCEL/excelproj2/Courses.xlsx
@@ -1,38 +1,122 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\moham\Desktop\data-analysis-proj\__EXCEL\excelproj2\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1996180-6AD8-4673-BDE4-B059C7E6F6AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Course_Master" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructors" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Course_Master" sheetId="1" r:id="rId1"/>
+    <sheet name="Instructors" sheetId="2" r:id="rId2"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="20">
+  <si>
+    <t>Course_ID</t>
+  </si>
+  <si>
+    <t>Course_Name</t>
+  </si>
+  <si>
+    <t>Fee</t>
+  </si>
+  <si>
+    <t>Instructor_ID</t>
+  </si>
+  <si>
+    <t>C01</t>
+  </si>
+  <si>
+    <t>Data Analytics</t>
+  </si>
+  <si>
+    <t>I01</t>
+  </si>
+  <si>
+    <t>C02</t>
+  </si>
+  <si>
+    <t>Full Stack</t>
+  </si>
+  <si>
+    <t>I02</t>
+  </si>
+  <si>
+    <t>C03</t>
+  </si>
+  <si>
+    <t>Data Science</t>
+  </si>
+  <si>
+    <t>C04</t>
+  </si>
+  <si>
+    <t>AI &amp; ML</t>
+  </si>
+  <si>
+    <t>I03</t>
+  </si>
+  <si>
+    <t>Instructor_Name</t>
+  </si>
+  <si>
+    <t>Experience_Years</t>
+  </si>
+  <si>
+    <t>Rahul</t>
+  </si>
+  <si>
+    <t>Priya</t>
+  </si>
+  <si>
+    <t>Amit</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -47,94 +131,164 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="4">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="8">
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+      </border>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4083AAEB-F9B4-4FA8-8EC4-B56BEE8714EE}" name="Course_Master" displayName="Course_Master" ref="A1:D5" totalsRowShown="0" headerRowDxfId="5" headerRowBorderDxfId="6" tableBorderDxfId="7">
+  <autoFilter ref="A1:D5" xr:uid="{4083AAEB-F9B4-4FA8-8EC4-B56BEE8714EE}"/>
+  <tableColumns count="4">
+    <tableColumn id="1" xr3:uid="{83E5072B-0557-4F06-80F7-12C7D2CA0960}" name="Course_ID" dataDxfId="0"/>
+    <tableColumn id="2" xr3:uid="{8D559ADA-2A68-456C-8F66-3E1B1F97CF2F}" name="Course_Name"/>
+    <tableColumn id="3" xr3:uid="{4F0E77B2-70A8-494B-9CDA-EDBCFBF251B7}" name="Fee"/>
+    <tableColumn id="4" xr3:uid="{1F7AFF29-5ED7-41A2-B5DC-8A42DA0FA79C}" name="Instructor_ID" dataDxfId="1"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{C7AE0097-C5D1-4450-94BB-7279910184D0}" name="Instructors" displayName="Instructors" ref="A1:C4" totalsRowShown="0" headerRowDxfId="2" headerRowBorderDxfId="3" tableBorderDxfId="4">
+  <autoFilter ref="A1:C4" xr:uid="{C7AE0097-C5D1-4450-94BB-7279910184D0}"/>
+  <tableColumns count="3">
+    <tableColumn id="1" xr3:uid="{1B2F3876-6122-4BE9-A580-8CC16CDAACE1}" name="Instructor_ID"/>
+    <tableColumn id="2" xr3:uid="{3FA5A724-BA1D-4B1C-A934-8E3099D57846}" name="Instructor_Name"/>
+    <tableColumn id="3" xr3:uid="{30FA2B3D-4602-4C61-90B5-152AC67252AD}" name="Experience_Years"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -421,193 +575,153 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="14.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17" style="2" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Course_ID</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Course_Name</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Fee</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Instructor_ID</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>C01</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Data Analytics</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2">
         <v>5000</v>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>I01</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>C02</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Full Stack</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
+      <c r="D2" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3">
         <v>7000</v>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>I02</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>C03</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Data Science</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
+      <c r="D3" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4">
         <v>9000</v>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>I01</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>C04</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>AI &amp; ML</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
+      <c r="D4" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5">
         <v>12000</v>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>I03</t>
-        </is>
+      <c r="D5" s="2" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="14.5703125" customWidth="1"/>
+    <col min="2" max="2" width="18" customWidth="1"/>
+    <col min="3" max="3" width="18.85546875" customWidth="1"/>
+    <col min="6" max="6" width="11" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Instructor_ID</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Instructor_Name</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Experience_Years</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>I01</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Rahul</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2">
         <v>8</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>I02</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Priya</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3">
         <v>5</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>I03</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Amit</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4">
         <v>10</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>